--- a/scripts/puzzle_bank.xlsx
+++ b/scripts/puzzle_bank.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L374"/>
+  <dimension ref="A1:L338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>2.319383</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
@@ -814,9 +814,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G9" s="1" t="n">
-        <v>46251</v>
-      </c>
+      <c r="G9" s="1" t="n"/>
       <c r="H9" t="n">
         <v>189</v>
       </c>
@@ -825,11 +823,6 @@
       </c>
       <c r="J9" t="n">
         <v>8</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>core,cover,vector,convert,contrive</t>
-        </is>
       </c>
       <c r="L9">
         <f>IF(C9="","Excluded (no APD)",IF(C9&lt;1.25,"Easy",IF(C9&lt;=2.8,"Medium",IF(C9&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
@@ -7691,7 +7684,7 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="D169" t="n">
         <v>4</v>
@@ -7706,9 +7699,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G169" s="1" t="n">
-        <v>46250</v>
-      </c>
+      <c r="G169" s="1" t="n"/>
       <c r="H169" t="n">
         <v>184</v>
       </c>
@@ -7717,11 +7708,6 @@
       </c>
       <c r="J169" t="n">
         <v>11</v>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>inter,cretin,noticer,reaction,fornicate,refraction,refractions</t>
-        </is>
       </c>
       <c r="L169">
         <f>IF(C170="","Excluded (no APD)",IF(C170&lt;1.25,"Easy",IF(C170&lt;=2.8,"Medium",IF(C170&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
@@ -7824,7 +7810,7 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="D172" t="n">
         <v>3</v>
@@ -7839,9 +7825,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G172" s="1" t="n">
-        <v>46252</v>
-      </c>
+      <c r="G172" s="1" t="n"/>
       <c r="H172" t="n">
         <v>186</v>
       </c>
@@ -7850,11 +7834,6 @@
       </c>
       <c r="J172" t="n">
         <v>9</v>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>tab,bats,boast,batons,obtains,botanist,obstinate</t>
-        </is>
       </c>
       <c r="L172">
         <f>IF(C173="","Excluded (no APD)",IF(C173&lt;1.25,"Easy",IF(C173&lt;=2.8,"Medium",IF(C173&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
@@ -8767,7 +8746,7 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>2</v>
+        <v>999.0018999999995</v>
       </c>
       <c r="D194" t="n">
         <v>999</v>
@@ -8782,9 +8761,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G194" s="1" t="n">
-        <v>46249</v>
-      </c>
+      <c r="G194" s="1" t="n"/>
       <c r="H194" t="n">
         <v>212</v>
       </c>
@@ -8793,11 +8770,6 @@
       </c>
       <c r="J194" t="n">
         <v>9</v>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>ailing,tailing,vigilant,violating</t>
-        </is>
       </c>
       <c r="L194">
         <f>IF(C195="","Excluded (no APD)",IF(C195&lt;1.25,"Easy",IF(C195&lt;=2.8,"Medium",IF(C195&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
@@ -8858,7 +8830,7 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>2</v>
+        <v>999.0020999999995</v>
       </c>
       <c r="D196" t="n">
         <v>999</v>
@@ -8873,9 +8845,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G196" s="1" t="n">
-        <v>46250</v>
-      </c>
+      <c r="G196" s="1" t="n"/>
       <c r="H196" t="n">
         <v>214</v>
       </c>
@@ -8884,11 +8854,6 @@
       </c>
       <c r="J196" t="n">
         <v>8</v>
-      </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>sip,tips,spite,sprite,respite,prestige</t>
-        </is>
       </c>
       <c r="L196">
         <f>IF(C197="","Excluded (no APD)",IF(C197&lt;1.25,"Easy",IF(C197&lt;=2.8,"Medium",IF(C197&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
@@ -9327,7 +9292,7 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>2</v>
+        <v>999.0031999999992</v>
       </c>
       <c r="D207" t="n">
         <v>999</v>
@@ -9342,9 +9307,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G207" s="1" t="n">
-        <v>46247</v>
-      </c>
+      <c r="G207" s="1" t="n"/>
       <c r="H207" t="n">
         <v>225</v>
       </c>
@@ -9353,11 +9316,6 @@
       </c>
       <c r="J207" t="n">
         <v>8</v>
-      </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>set,rest,terms,muster,mutters,trumpets</t>
-        </is>
       </c>
       <c r="L207">
         <f>IF(C208="","Excluded (no APD)",IF(C208&lt;1.25,"Easy",IF(C208&lt;=2.8,"Medium",IF(C208&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
@@ -13528,37 +13486,42 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>cab</t>
+          <t>if</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>scarab</t>
+          <t>fixer</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="D306" t="n">
         <v>1</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>rookie</t>
+          <t>beginner</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G306" s="1" t="n">
-        <v>46247</v>
+        <v>46272</v>
       </c>
       <c r="I306" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J306" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>cab,crab,crabs,scarab</t>
+          <t>if,fir,fire,fixer</t>
         </is>
       </c>
       <c r="L306">
@@ -13569,37 +13532,42 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>vine</t>
+          <t>bid</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>traveling</t>
+          <t>builder</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="D307" t="n">
+        <v>2</v>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G307" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="I307" t="n">
         <v>3</v>
       </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>expert</t>
-        </is>
-      </c>
-      <c r="G307" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="I307" t="n">
-        <v>4</v>
-      </c>
       <c r="J307" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>vine,naive,native,vintage,valeting,traveling</t>
+          <t>bid,bird,bride,bridle,builder</t>
         </is>
       </c>
       <c r="L307">
@@ -13610,37 +13578,42 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>elf</t>
+          <t>gee</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>designer</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="D308" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>rookie</t>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G308" s="1" t="n">
-        <v>46248</v>
+        <v>46272</v>
       </c>
       <c r="I308" t="n">
         <v>3</v>
       </c>
       <c r="J308" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>elf,file,filet,filter</t>
+          <t>gee,gene,green,gender,genders,designer</t>
         </is>
       </c>
       <c r="L308">
@@ -13651,37 +13624,42 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>tide</t>
+          <t>ow</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>dentistry</t>
+          <t>cower</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="D309" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>novice</t>
+          <t>beginner</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G309" s="1" t="n">
-        <v>46248</v>
+        <v>46273</v>
       </c>
       <c r="I309" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J309" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>tide,tried,tinder,trident,tridents,dentistry</t>
+          <t>ow,cow,crow,cower</t>
         </is>
       </c>
       <c r="L309">
@@ -13692,37 +13670,42 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>intent</t>
+          <t>he</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>intestine</t>
+          <t>hoarse</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="D310" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>expert</t>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G310" s="1" t="n">
-        <v>46248</v>
+        <v>46273</v>
       </c>
       <c r="I310" t="n">
+        <v>2</v>
+      </c>
+      <c r="J310" t="n">
         <v>6</v>
       </c>
-      <c r="J310" t="n">
-        <v>9</v>
-      </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>intent,intents,sentient,intestine</t>
+          <t>he,she,shoe,horse,hoarse</t>
         </is>
       </c>
       <c r="L310">
@@ -13733,37 +13716,42 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>cap</t>
+          <t>at</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>camper</t>
+          <t>tractor</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="D311" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>rookie</t>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G311" s="1" t="n">
-        <v>46249</v>
+        <v>46273</v>
       </c>
       <c r="I311" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J311" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>cap,pace,recap,camper</t>
+          <t>at,rat,cart,actor,carrot,tractor</t>
         </is>
       </c>
       <c r="L311">
@@ -13774,37 +13762,42 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>am</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>destruction</t>
+          <t>tamed</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="D312" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>expert</t>
+          <t>beginner</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G312" s="1" t="n">
-        <v>46249</v>
+        <v>46274</v>
       </c>
       <c r="I312" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J312" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>unit,tunic,induct,conduit,discount,seduction,reductions,destruction</t>
+          <t>am,mat,meat,tamed</t>
         </is>
       </c>
       <c r="L312">
@@ -13815,27 +13808,32 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>if</t>
+          <t>so</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>finger</t>
+          <t>rosary</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="D313" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>rookie</t>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G313" s="1" t="n">
-        <v>46250</v>
+        <v>46274</v>
       </c>
       <c r="I313" t="n">
         <v>2</v>
@@ -13845,7 +13843,7 @@
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>if,fin,fine,finer,finger</t>
+          <t>so,soy,rosy,sorry,rosary</t>
         </is>
       </c>
       <c r="L313">
@@ -13856,37 +13854,42 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>ors</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>casket</t>
+          <t>oranges</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="D314" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>rookie</t>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G314" s="1" t="n">
-        <v>46251</v>
+        <v>46274</v>
       </c>
       <c r="I314" t="n">
         <v>3</v>
       </c>
       <c r="J314" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t>ask,sake,steak,casket</t>
+          <t>ors,oars,sonar,organs,oranges</t>
         </is>
       </c>
       <c r="L314">
@@ -13897,37 +13900,42 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>love</t>
+          <t>peen</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>volatile</t>
+          <t>penned</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="D315" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>expert</t>
+          <t>beginner</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G315" s="1" t="n">
-        <v>46251</v>
+        <v>46275</v>
       </c>
       <c r="I315" t="n">
         <v>4</v>
       </c>
       <c r="J315" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>love,olive,violet,violate,volatile</t>
+          <t>peen,penne,penned</t>
         </is>
       </c>
       <c r="L315">
@@ -13938,37 +13946,42 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>duo</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>heard</t>
+          <t>abound</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="D316" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>rookie</t>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G316" s="1" t="n">
-        <v>46252</v>
+        <v>46275</v>
       </c>
       <c r="I316" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J316" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>ad,had,head,heard</t>
+          <t>duo,udon,bound,abound</t>
         </is>
       </c>
       <c r="L316">
@@ -13979,37 +13992,42 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>due</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>unbathed</t>
+          <t>originate</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="D317" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>novice</t>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G317" s="1" t="n">
-        <v>46252</v>
+        <v>46275</v>
       </c>
       <c r="I317" t="n">
         <v>3</v>
       </c>
       <c r="J317" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>due,dune,tuned,hunted,haunted,unbathed</t>
+          <t>tag,gnat,grant,rating,orating,rigatoni,originate</t>
         </is>
       </c>
       <c r="L317">
@@ -14020,27 +14038,32 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>at</t>
+          <t>pa</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>track</t>
+          <t>clamp</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="D318" t="n">
         <v>1</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>rookie</t>
+          <t>beginner</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G318" s="1" t="n">
-        <v>46253</v>
+        <v>46276</v>
       </c>
       <c r="I318" t="n">
         <v>2</v>
@@ -14050,7 +14073,7 @@
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>at,cat,cart,track</t>
+          <t>pa,pal,lamp,clamp</t>
         </is>
       </c>
       <c r="L318">
@@ -14061,16 +14084,16 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>pea</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>garlics</t>
+          <t>pirates</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="D319" t="n">
         <v>2</v>
@@ -14080,18 +14103,23 @@
           <t>novice</t>
         </is>
       </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G319" s="1" t="n">
-        <v>46253</v>
+        <v>46276</v>
       </c>
       <c r="I319" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J319" t="n">
         <v>7</v>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>is,sir,airs,rails,grails,garlics</t>
+          <t>pea,pear,spare,praise,pirates</t>
         </is>
       </c>
       <c r="L319">
@@ -14102,16 +14130,16 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>air</t>
+          <t>me</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>terrain</t>
+          <t>heroism</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="D320" t="n">
         <v>3</v>
@@ -14121,18 +14149,23 @@
           <t>expert</t>
         </is>
       </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G320" s="1" t="n">
-        <v>46253</v>
+        <v>46276</v>
       </c>
       <c r="I320" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J320" t="n">
         <v>7</v>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>air,rain,train,retina,terrain</t>
+          <t>me,hem,home,homer,homier,heroism</t>
         </is>
       </c>
       <c r="L320">
@@ -14143,27 +14176,32 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>as</t>
+          <t>go</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>forge</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="D321" t="n">
         <v>1</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>rookie</t>
+          <t>beginner</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G321" s="1" t="n">
-        <v>46254</v>
+        <v>46277</v>
       </c>
       <c r="I321" t="n">
         <v>2</v>
@@ -14173,7 +14211,7 @@
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>as,say,easy,years</t>
+          <t>go,fog,frog,forge</t>
         </is>
       </c>
       <c r="L321">
@@ -14184,16 +14222,16 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>dime</t>
+          <t>en</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>dummies</t>
+          <t>tinkle</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="D322" t="n">
         <v>2</v>
@@ -14203,18 +14241,23 @@
           <t>novice</t>
         </is>
       </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G322" s="1" t="n">
-        <v>46254</v>
+        <v>46277</v>
       </c>
       <c r="I322" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J322" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>dime,mimed,medium,dummies</t>
+          <t>en,ten,lent,inlet,tinkle</t>
         </is>
       </c>
       <c r="L322">
@@ -14225,16 +14268,16 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>rue</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>thrashed</t>
+          <t>flounder</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="D323" t="n">
         <v>3</v>
@@ -14244,18 +14287,23 @@
           <t>expert</t>
         </is>
       </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G323" s="1" t="n">
-        <v>46254</v>
+        <v>46277</v>
       </c>
       <c r="I323" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J323" t="n">
         <v>8</v>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>ad,had,hard,heard,shared,trashed,thrashed</t>
+          <t>rue,rude,under,refund,founder,flounder</t>
         </is>
       </c>
       <c r="L323">
@@ -14266,27 +14314,32 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>on</t>
+          <t>or</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>clone</t>
+          <t>boxer</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="D324" t="n">
         <v>1</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>rookie</t>
+          <t>beginner</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G324" s="1" t="n">
-        <v>46255</v>
+        <v>46278</v>
       </c>
       <c r="I324" t="n">
         <v>2</v>
@@ -14296,7 +14349,7 @@
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>on,one,cone,clone</t>
+          <t>or,ore,robe,boxer</t>
         </is>
       </c>
       <c r="L324">
@@ -14307,16 +14360,16 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>cut</t>
+          <t>tad</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>curate</t>
+          <t>tadpole</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="D325" t="n">
         <v>2</v>
@@ -14326,18 +14379,23 @@
           <t>novice</t>
         </is>
       </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G325" s="1" t="n">
-        <v>46255</v>
+        <v>46278</v>
       </c>
       <c r="I325" t="n">
         <v>3</v>
       </c>
       <c r="J325" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>cut,cute,acute,curate</t>
+          <t>tad,date,dealt,plated,tadpole</t>
         </is>
       </c>
       <c r="L325">
@@ -14348,16 +14406,16 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>son</t>
+          <t>louden</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>jointers</t>
+          <t>convulsed</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="D326" t="n">
         <v>3</v>
@@ -14367,18 +14425,23 @@
           <t>expert</t>
         </is>
       </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G326" s="1" t="n">
-        <v>46255</v>
+        <v>46278</v>
       </c>
       <c r="I326" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J326" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>son,nose,noise,nosier,rejoins,jointers</t>
+          <t>louden,unloved,unsolved,convulsed</t>
         </is>
       </c>
       <c r="L326">
@@ -14389,201 +14452,369 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>bar</t>
+          <t>at</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>barked</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C327" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D327" t="n">
         <v>1</v>
       </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>beginner</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G327" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="I327" t="n">
+        <v>2</v>
+      </c>
+      <c r="J327" t="n">
+        <v>5</v>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>bar,bear,bread,barked</t>
-        </is>
+          <t>at,tar,tear,water</t>
+        </is>
+      </c>
+      <c r="L327">
+        <f>IF(C327="","Excluded (no APD)",IF(C327&lt;1.25,"Easy",IF(C327&lt;=2.8,"Medium",IF(C327&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>rot</t>
+          <t>ale</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>smoother</t>
+          <t>clapped</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
+        <v>2.1</v>
+      </c>
+      <c r="D328" t="n">
+        <v>2</v>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G328" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="I328" t="n">
+        <v>3</v>
+      </c>
+      <c r="J328" t="n">
+        <v>7</v>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>rot,sort,short,others,mothers,smoother</t>
-        </is>
+          <t>ale,pale,apple,lapped,clapped</t>
+        </is>
+      </c>
+      <c r="L328">
+        <f>IF(C328="","Excluded (no APD)",IF(C328&lt;1.25,"Easy",IF(C328&lt;=2.8,"Medium",IF(C328&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>me</t>
+          <t>louden</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>convulsed</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
+        <v>3.1</v>
+      </c>
+      <c r="D329" t="n">
+        <v>3</v>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G329" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="I329" t="n">
+        <v>6</v>
+      </c>
+      <c r="J329" t="n">
+        <v>9</v>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>me,men,mine,anime,median,mediant,dominate,mediation,medication</t>
-        </is>
+          <t>louden,unloved,unsolved,convulsed</t>
+        </is>
+      </c>
+      <c r="L329">
+        <f>IF(C329="","Excluded (no APD)",IF(C329&lt;1.25,"Easy",IF(C329&lt;=2.8,"Medium",IF(C329&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>at</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>thank</t>
+          <t>dread</t>
         </is>
       </c>
       <c r="C330" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D330" t="n">
         <v>1</v>
       </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>beginner</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G330" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="I330" t="n">
+        <v>2</v>
+      </c>
+      <c r="J330" t="n">
+        <v>5</v>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t>at,tan,tank,thank</t>
-        </is>
+          <t>ad,add,dead,dread</t>
+        </is>
+      </c>
+      <c r="L330">
+        <f>IF(C330="","Excluded (no APD)",IF(C330&lt;1.25,"Easy",IF(C330&lt;=2.8,"Medium",IF(C330&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>sate</t>
+          <t>us</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>masteries</t>
+          <t>plumes</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>2</v>
-      </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
+        <v>2.1</v>
+      </c>
+      <c r="D331" t="n">
+        <v>2</v>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G331" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="I331" t="n">
+        <v>2</v>
+      </c>
+      <c r="J331" t="n">
+        <v>6</v>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>sate,stare,stream,steamer,steamers,masteries</t>
-        </is>
+          <t>us,pus,plus,pulse,plumes</t>
+        </is>
+      </c>
+      <c r="L331">
+        <f>IF(C331="","Excluded (no APD)",IF(C331&lt;1.25,"Easy",IF(C331&lt;=2.8,"Medium",IF(C331&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>lee</t>
+          <t>us</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>reclaimed</t>
+          <t>supreme</t>
         </is>
       </c>
       <c r="C332" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D332" t="n">
         <v>3</v>
       </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G332" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="I332" t="n">
+        <v>2</v>
+      </c>
+      <c r="J332" t="n">
+        <v>7</v>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t>lee,leer,elder,dealer,emerald,remedial,reclaimed</t>
-        </is>
+          <t>us,sum,muse,serum,resume,supreme</t>
+        </is>
+      </c>
+      <c r="L332">
+        <f>IF(C332="","Excluded (no APD)",IF(C332&lt;1.25,"Easy",IF(C332&lt;=2.8,"Medium",IF(C332&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>is</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>widen</t>
+          <t>spine</t>
         </is>
       </c>
       <c r="C333" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D333" t="n">
         <v>1</v>
       </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>beginner</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G333" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="I333" t="n">
+        <v>2</v>
+      </c>
+      <c r="J333" t="n">
+        <v>5</v>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>in,win,wind,widen</t>
-        </is>
+          <t>is,sin,snip,spine</t>
+        </is>
+      </c>
+      <c r="L333">
+        <f>IF(C333="","Excluded (no APD)",IF(C333&lt;1.25,"Easy",IF(C333&lt;=2.8,"Medium",IF(C333&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>ear</t>
+          <t>is</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>lateral</t>
+          <t>stride</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
+        <v>2.1</v>
+      </c>
+      <c r="D334" t="n">
+        <v>2</v>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G334" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="I334" t="n">
+        <v>2</v>
+      </c>
+      <c r="J334" t="n">
+        <v>6</v>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>ear,real,alter,taller,lateral</t>
-        </is>
+          <t>is,sir,sire,rides,stride</t>
+        </is>
+      </c>
+      <c r="L334">
+        <f>IF(C334="","Excluded (no APD)",IF(C334&lt;1.25,"Easy",IF(C334&lt;=2.8,"Medium",IF(C334&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
       </c>
     </row>
     <row r="335">
@@ -14594,996 +14825,180 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>flustering</t>
+          <t>perusing</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
+        <v>3.1</v>
+      </c>
+      <c r="D335" t="n">
+        <v>3</v>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G335" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="I335" t="n">
+        <v>2</v>
+      </c>
+      <c r="J335" t="n">
+        <v>8</v>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>is,sin,sing,sting,string,rusting,rustling,resulting,flustering</t>
-        </is>
+          <t>is,sin,sing,using,genius,reusing,perusing</t>
+        </is>
+      </c>
+      <c r="L335">
+        <f>IF(C335="","Excluded (no APD)",IF(C335&lt;1.25,"Easy",IF(C335&lt;=2.8,"Medium",IF(C335&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>he</t>
+          <t>to</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>heart</t>
+          <t>boast</t>
         </is>
       </c>
       <c r="C336" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D336" t="n">
         <v>1</v>
       </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>beginner</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G336" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="I336" t="n">
+        <v>2</v>
+      </c>
+      <c r="J336" t="n">
+        <v>5</v>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>he,the,heat,heart</t>
-        </is>
+          <t>to,bot,boat,boast</t>
+        </is>
+      </c>
+      <c r="L336">
+        <f>IF(C336="","Excluded (no APD)",IF(C336&lt;1.25,"Easy",IF(C336&lt;=2.8,"Medium",IF(C336&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>as</t>
+          <t>so</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>sneaky</t>
+          <t>drowns</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
+        <v>2.1</v>
+      </c>
+      <c r="D337" t="n">
+        <v>2</v>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G337" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="I337" t="n">
+        <v>2</v>
+      </c>
+      <c r="J337" t="n">
+        <v>6</v>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>as,sea,sake,snake,sneaky</t>
-        </is>
+          <t>so,sow,rows,sword,drowns</t>
+        </is>
+      </c>
+      <c r="L337">
+        <f>IF(C337="","Excluded (no APD)",IF(C337&lt;1.25,"Easy",IF(C337&lt;=2.8,"Medium",IF(C337&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>ma</t>
+          <t>anti</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>inflame</t>
+          <t>fornicate</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
+        <v>3.1</v>
+      </c>
+      <c r="D338" t="n">
+        <v>3</v>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G338" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="I338" t="n">
+        <v>4</v>
+      </c>
+      <c r="J338" t="n">
+        <v>9</v>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>ma,man,main,anime,famine,inflame</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>by</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>bossy</t>
-        </is>
-      </c>
-      <c r="C339" t="n">
-        <v>1</v>
-      </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="K339" t="inlineStr">
-        <is>
-          <t>by,boy,boys,bossy</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>lid</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>bridle</t>
-        </is>
-      </c>
-      <c r="C340" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="K340" t="inlineStr">
-        <is>
-          <t>lid,deli,riled,bridle</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>unctions</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>continuous</t>
-        </is>
-      </c>
-      <c r="C341" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="K341" t="inlineStr">
-        <is>
-          <t>unctions,contusion,continuous</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>fin</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>friend</t>
-        </is>
-      </c>
-      <c r="C342" t="n">
-        <v>1</v>
-      </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="K342" t="inlineStr">
-        <is>
-          <t>fin,find,fined,friend</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>collage</t>
-        </is>
-      </c>
-      <c r="C343" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="K343" t="inlineStr">
-        <is>
-          <t>all,call,local,locale,collage</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>an</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>bargeman</t>
-        </is>
-      </c>
-      <c r="C344" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="K344" t="inlineStr">
-        <is>
-          <t>an,ran,rang,anger,manger,manager,bargeman</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>ski</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>sticky</t>
-        </is>
-      </c>
-      <c r="C345" t="n">
-        <v>1</v>
-      </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="K345" t="inlineStr">
-        <is>
-          <t>ski,sick,stick,sticky</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>wine</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>swindler</t>
-        </is>
-      </c>
-      <c r="C346" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="K346" t="inlineStr">
-        <is>
-          <t>wine,swine,widens,rewinds,swindler</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>rise</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>compilers</t>
-        </is>
-      </c>
-      <c r="C347" t="n">
-        <v>3</v>
-      </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="K347" t="inlineStr">
-        <is>
-          <t>rise,pries,primes,promise,implores,compilers</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>rid</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>driven</t>
-        </is>
-      </c>
-      <c r="C348" t="n">
-        <v>1</v>
-      </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="K348" t="inlineStr">
-        <is>
-          <t>rid,ride,diver,driven</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>bristle</t>
-        </is>
-      </c>
-      <c r="C349" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="K349" t="inlineStr">
-        <is>
-          <t>best,bites,tribes,bristle</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>wig</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>withering</t>
-        </is>
-      </c>
-      <c r="C350" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="G350" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="K350" t="inlineStr">
-        <is>
-          <t>wig,wing,wring,wiring,writing,writhing,withering</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>of</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>floor</t>
-        </is>
-      </c>
-      <c r="C351" t="n">
-        <v>1</v>
-      </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="K351" t="inlineStr">
-        <is>
-          <t>of,for,roof,floor</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>oat</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>flotsam</t>
-        </is>
-      </c>
-      <c r="C352" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="K352" t="inlineStr">
-        <is>
-          <t>oat,atom,moats,almost,flotsam</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>tire</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>ministries</t>
-        </is>
-      </c>
-      <c r="C353" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="G353" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="K353" t="inlineStr">
-        <is>
-          <t>tire,inter,tinier,mintier,minister,ministers,ministries</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>crown</t>
-        </is>
-      </c>
-      <c r="C354" t="n">
-        <v>1</v>
-      </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="K354" t="inlineStr">
-        <is>
-          <t>on,now,worn,crown</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>me</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>monkey</t>
-        </is>
-      </c>
-      <c r="C355" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G355" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="K355" t="inlineStr">
-        <is>
-          <t>me,men,omen,money,monkey</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>girl</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>ridgeline</t>
-        </is>
-      </c>
-      <c r="C356" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="K356" t="inlineStr">
-        <is>
-          <t>girl,liger,linger,reeling,lingered,ridgeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>go</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>lodge</t>
-        </is>
-      </c>
-      <c r="C357" t="n">
-        <v>1</v>
-      </c>
-      <c r="G357" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="K357" t="inlineStr">
-        <is>
-          <t>go,dog,gold,lodge</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>ye</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>pretty</t>
-        </is>
-      </c>
-      <c r="C358" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="K358" t="inlineStr">
-        <is>
-          <t>ye,yet,type,petty,pretty</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>traveling</t>
-        </is>
-      </c>
-      <c r="C359" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="K359" t="inlineStr">
-        <is>
-          <t>age,gear,anger,regain,tangier,averting,traveling</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>blink</t>
-        </is>
-      </c>
-      <c r="C360" t="n">
-        <v>1</v>
-      </c>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="K360" t="inlineStr">
-        <is>
-          <t>in,ink,link,blink</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>per</t>
-        </is>
-      </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>scooper</t>
-        </is>
-      </c>
-      <c r="C361" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G361" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="K361" t="inlineStr">
-        <is>
-          <t>per,rope,spore,corpse,scooper</t>
-        </is>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>air</t>
-        </is>
-      </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>pyramid</t>
-        </is>
-      </c>
-      <c r="C362" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G362" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="K362" t="inlineStr">
-        <is>
-          <t>air,raid,dairy,myriad,pyramid</t>
-        </is>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>by</t>
-        </is>
-      </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>tabby</t>
-        </is>
-      </c>
-      <c r="C363" t="n">
-        <v>1</v>
-      </c>
-      <c r="G363" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="K363" t="inlineStr">
-        <is>
-          <t>by,bay,baby,tabby</t>
-        </is>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>lie</t>
-        </is>
-      </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>literary</t>
-        </is>
-      </c>
-      <c r="C364" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G364" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="K364" t="inlineStr">
-        <is>
-          <t>lie,rile,relit,retail,trailer,literary</t>
-        </is>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>ruminates</t>
-        </is>
-      </c>
-      <c r="C365" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="G365" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="K365" t="inlineStr">
-        <is>
-          <t>sun,stun,tunes,tuners,saunter,urinates,ruminates</t>
-        </is>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>at</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>chant</t>
-        </is>
-      </c>
-      <c r="C366" t="n">
-        <v>1</v>
-      </c>
-      <c r="G366" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="K366" t="inlineStr">
-        <is>
-          <t>at,cat,chat,chant</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>renown</t>
-        </is>
-      </c>
-      <c r="C367" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G367" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="K367" t="inlineStr">
-        <is>
-          <t>new,wren,owner,renown</t>
-        </is>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>rant</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>decorating</t>
-        </is>
-      </c>
-      <c r="C368" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="G368" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="K368" t="inlineStr">
-        <is>
-          <t>rant,train,rating,ingrate,treading,redacting,decorating</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>an</t>
-        </is>
-      </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
-      </c>
-      <c r="C369" t="n">
-        <v>1</v>
-      </c>
-      <c r="G369" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="K369" t="inlineStr">
-        <is>
-          <t>an,ban,bank,blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>maul</t>
-        </is>
-      </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>lumbar</t>
-        </is>
-      </c>
-      <c r="C370" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G370" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="K370" t="inlineStr">
-        <is>
-          <t>maul,album,lumbar</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>tag</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>nostalgic</t>
-        </is>
-      </c>
-      <c r="C371" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="G371" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="K371" t="inlineStr">
-        <is>
-          <t>tag,gait,giant,acting,casting,coasting,nostalgic</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>is</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>fishy</t>
-        </is>
-      </c>
-      <c r="C372" t="n">
-        <v>1</v>
-      </c>
-      <c r="G372" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="K372" t="inlineStr">
-        <is>
-          <t>is,his,fish,fishy</t>
-        </is>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>mans</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>normals</t>
-        </is>
-      </c>
-      <c r="C373" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G373" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="K373" t="inlineStr">
-        <is>
-          <t>mans,moans,salmon,normals</t>
-        </is>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>sane</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>readiness</t>
-        </is>
-      </c>
-      <c r="C374" t="n">
-        <v>3</v>
-      </c>
-      <c r="G374" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="K374" t="inlineStr">
-        <is>
-          <t>sane,nears,snared,sandier,sardines,readiness</t>
-        </is>
+          <t>anti,antic,action,faction,fraction,fornicate</t>
+        </is>
+      </c>
+      <c r="L338">
+        <f>IF(C338="","Excluded (no APD)",IF(C338&lt;1.25,"Easy",IF(C338&lt;=2.8,"Medium",IF(C338&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
       </c>
     </row>
   </sheetData>
